--- a/input/reg_partnership.xlsx
+++ b/input/reg_partnership.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="416" uniqueCount="87">
   <si>
     <t>Description:</t>
   </si>
@@ -283,7 +283,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="15">
+  <fonts count="29">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -351,6 +351,76 @@
       <name val="Calibri"/>
       <b/>
     </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -360,7 +430,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="8">
+  <borders count="15">
     <border>
       <left/>
       <right/>
@@ -417,11 +487,60 @@
       <bottom style="none"/>
       <diagonal style="none"/>
     </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
@@ -451,6 +570,34 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="10" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="11" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="12" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="13" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="14" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -464,7 +611,7 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
@@ -485,10 +632,10 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="s">
+      <c r="A5" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="10" t="s">
         <v>0</v>
       </c>
     </row>
@@ -509,7 +656,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="s">
+      <c r="A10" s="11" t="s">
         <v>10</v>
       </c>
       <c r="B10" t="s">
@@ -536,12 +683,12 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="12" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="6" t="s">
+      <c r="A3" s="13" t="s">
         <v>62</v>
       </c>
     </row>
@@ -574,7 +721,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="7" t="s">
+      <c r="A7" s="14" t="s">
         <v>86</v>
       </c>
     </row>
